--- a/marketing/Продвижение_чаты_дайджест.xlsx
+++ b/marketing/Продвижение_чаты_дайджест.xlsx
@@ -2720,7 +2720,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>- Ссылка на карточку события: https://armagedroid36-blip.github.io/events-map/#/?e=&lt;id события&gt;. Короткая и кликабельная.</t>
+          <t>- Ссылка на карточку события: https://mypins.site/#/?e=&lt;id события&gt;. Короткая и кликабельная.</t>
         </is>
       </c>
     </row>
